--- a/e2e/fixtures/cotizador-mini.xlsx
+++ b/e2e/fixtures/cotizador-mini.xlsx
@@ -4095,18 +4095,6 @@
       <c r="H72">
         <v>1.3</v>
       </c>
-      <c r="I72">
-        <v>4000</v>
-      </c>
-      <c r="J72">
-        <v>8000</v>
-      </c>
-      <c r="K72">
-        <v>1500</v>
-      </c>
-      <c r="L72">
-        <v>1500</v>
-      </c>
       <c r="M72">
         <v>15000</v>
       </c>
